--- a/database/teaching.xlsx
+++ b/database/teaching.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -315,6 +315,18 @@
   </si>
   <si>
     <t>https://caligiu.github.io/Pupillometry_ARCA2025/</t>
+  </si>
+  <si>
+    <t>Introduction to GLM (workshop)</t>
+  </si>
+  <si>
+    <t>Margherita Calderan, Filippo Gambarota</t>
+  </si>
+  <si>
+    <t>Introductory workshop about Generalized Linear Models (logistic regression)</t>
+  </si>
+  <si>
+    <t>https://psicostat.github.io/glm-workshop/</t>
   </si>
 </sst>
 </file>
@@ -618,7 +630,7 @@
     <col customWidth="1" min="6" max="6" width="27.25"/>
     <col customWidth="1" min="7" max="7" width="11.88"/>
     <col customWidth="1" min="8" max="8" width="9.13"/>
-    <col customWidth="1" min="9" max="9" width="16.63"/>
+    <col customWidth="1" min="9" max="9" width="26.13"/>
     <col customWidth="1" min="10" max="10" width="28.5"/>
     <col customWidth="1" min="11" max="11" width="23.5"/>
     <col customWidth="1" min="12" max="12" width="71.13"/>
@@ -1336,8 +1348,42 @@
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="4">
+        <v>30.0</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="8"/>
@@ -5246,7 +5292,7 @@
   </sheetData>
   <autoFilter ref="$A$1:$AD$996"/>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G20">
       <formula1>"Inglese,Italiano"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5265,10 +5311,11 @@
     <hyperlink r:id="rId12" ref="L17"/>
     <hyperlink r:id="rId13" ref="L18"/>
     <hyperlink r:id="rId14" ref="L19"/>
+    <hyperlink r:id="rId15" ref="L20"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
--- a/database/teaching.xlsx
+++ b/database/teaching.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>PhD-level Structural Equation Modeling, theory, estimation, and applied modeling with observed and latent variables</t>
+  </si>
+  <si>
+    <t>https://feracotommaso.github.io/SEM-phd-course/</t>
   </si>
   <si>
     <t>Basics of R for Data Science</t>
@@ -823,6 +826,9 @@
       <c r="K5" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="L5" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2">
@@ -832,7 +838,7 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>21</v>
@@ -853,13 +859,13 @@
         <v>23</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -870,10 +876,10 @@
         <v>1.0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4">
         <v>20.0</v>
@@ -882,7 +888,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="4">
         <v>10.0</v>
@@ -891,13 +897,13 @@
         <v>16</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -908,10 +914,10 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="4">
         <v>3.0</v>
@@ -926,16 +932,16 @@
         <v>30.0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -946,7 +952,7 @@
         <v>1.0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
@@ -964,16 +970,16 @@
         <v>20.0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -984,10 +990,10 @@
         <v>1.0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" s="4">
         <v>5.0</v>
@@ -1005,13 +1011,13 @@
         <v>23</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -1022,10 +1028,10 @@
         <v>1.0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="4">
         <v>10.0</v>
@@ -1043,10 +1049,10 @@
         <v>23</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -1057,10 +1063,10 @@
         <v>1.0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="4">
         <v>10.0</v>
@@ -1078,10 +1084,10 @@
         <v>23</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -1092,10 +1098,10 @@
         <v>1.0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="4">
         <v>10.0</v>
@@ -1113,10 +1119,10 @@
         <v>23</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -1127,7 +1133,7 @@
         <v>1.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>13</v>
@@ -1136,10 +1142,10 @@
         <v>10.0</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14" s="4">
         <v>15.0</v>
@@ -1148,13 +1154,13 @@
         <v>16</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -1165,7 +1171,7 @@
         <v>1.0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
@@ -1183,16 +1189,16 @@
         <v>40.0</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1203,10 +1209,10 @@
         <v>1.0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="4">
         <v>20.0</v>
@@ -1215,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H16" s="4">
         <v>10.0</v>
@@ -1224,13 +1230,13 @@
         <v>16</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -1241,10 +1247,10 @@
         <v>1.0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="4">
         <v>5.0</v>
@@ -1262,13 +1268,13 @@
         <v>23</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -1279,16 +1285,16 @@
         <v>1.0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18" s="4">
         <v>1.0</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>15</v>
@@ -1300,13 +1306,13 @@
         <v>16</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -1317,10 +1323,10 @@
         <v>1.0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E19" s="4">
         <v>20.0</v>
@@ -1338,13 +1344,13 @@
         <v>16</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -1355,16 +1361,16 @@
         <v>1.0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="4">
         <v>4.0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>15</v>
@@ -1373,16 +1379,16 @@
         <v>30.0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -5300,22 +5306,23 @@
     <hyperlink r:id="rId1" ref="L2"/>
     <hyperlink r:id="rId2" ref="L3"/>
     <hyperlink r:id="rId3" ref="L4"/>
-    <hyperlink r:id="rId4" ref="L6"/>
-    <hyperlink r:id="rId5" ref="L7"/>
-    <hyperlink r:id="rId6" ref="L8"/>
-    <hyperlink r:id="rId7" ref="L9"/>
-    <hyperlink r:id="rId8" ref="L10"/>
-    <hyperlink r:id="rId9" ref="L14"/>
-    <hyperlink r:id="rId10" ref="L15"/>
-    <hyperlink r:id="rId11" ref="L16"/>
-    <hyperlink r:id="rId12" ref="L17"/>
-    <hyperlink r:id="rId13" ref="L18"/>
-    <hyperlink r:id="rId14" ref="L19"/>
-    <hyperlink r:id="rId15" ref="L20"/>
+    <hyperlink r:id="rId4" ref="L5"/>
+    <hyperlink r:id="rId5" ref="L6"/>
+    <hyperlink r:id="rId6" ref="L7"/>
+    <hyperlink r:id="rId7" ref="L8"/>
+    <hyperlink r:id="rId8" ref="L9"/>
+    <hyperlink r:id="rId9" ref="L10"/>
+    <hyperlink r:id="rId10" ref="L14"/>
+    <hyperlink r:id="rId11" ref="L15"/>
+    <hyperlink r:id="rId12" ref="L16"/>
+    <hyperlink r:id="rId13" ref="L17"/>
+    <hyperlink r:id="rId14" ref="L18"/>
+    <hyperlink r:id="rId15" ref="L19"/>
+    <hyperlink r:id="rId16" ref="L20"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>